--- a/artfynd/A 57690-2022 artfynd.xlsx
+++ b/artfynd/A 57690-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57690-2022 artfynd.xlsx
+++ b/artfynd/A 57690-2022 artfynd.xlsx
@@ -2198,7 +2198,7 @@
         <v>126648791</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jonatan Axelsson, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Jonatan Axelsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 57690-2022 artfynd.xlsx
+++ b/artfynd/A 57690-2022 artfynd.xlsx
@@ -2198,7 +2198,7 @@
         <v>126648791</v>
       </c>
       <c r="B15" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Jonatan Axelsson</t>
+          <t>Jonatan Axelsson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 57690-2022 artfynd.xlsx
+++ b/artfynd/A 57690-2022 artfynd.xlsx
@@ -1948,12 +1948,7 @@
         <v>105911447</v>
       </c>
       <c r="B13" t="n">
-        <v>57508</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Dokumentation efterfrågas</t>
-        </is>
+        <v>56613</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,10 +1993,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541923.5576353129</v>
+        <v>541924</v>
       </c>
       <c r="R13" t="n">
-        <v>6507840.288822434</v>
+        <v>6507841</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2031,19 +2026,9 @@
           <t>2021-08-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 57690-2022 artfynd.xlsx
+++ b/artfynd/A 57690-2022 artfynd.xlsx
@@ -1948,7 +1948,7 @@
         <v>105911447</v>
       </c>
       <c r="B13" t="n">
-        <v>56613</v>
+        <v>56615</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 57690-2022 artfynd.xlsx
+++ b/artfynd/A 57690-2022 artfynd.xlsx
@@ -1948,7 +1948,7 @@
         <v>105911447</v>
       </c>
       <c r="B13" t="n">
-        <v>56615</v>
+        <v>56617</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 57690-2022 artfynd.xlsx
+++ b/artfynd/A 57690-2022 artfynd.xlsx
@@ -1948,7 +1948,7 @@
         <v>105911447</v>
       </c>
       <c r="B13" t="n">
-        <v>56617</v>
+        <v>56620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 57690-2022 artfynd.xlsx
+++ b/artfynd/A 57690-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3916143</v>
+        <v>97309085</v>
       </c>
       <c r="B2" t="n">
-        <v>99381</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221223</v>
+        <v>3884</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finspång, strax NV om Översätter, Ög</t>
+          <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541855.4368454639</v>
+        <v>541799</v>
       </c>
       <c r="R2" t="n">
-        <v>6507689.400664413</v>
+        <v>6507856</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-08-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-08-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,36 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>ek-hassellund</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Amanda Sjölund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Amanda Sjölund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5021320</v>
+        <v>97309087</v>
       </c>
       <c r="B3" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>6443</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Finspång, strax NV om Översätter, Ög</t>
+          <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541855.4368454639</v>
+        <v>541958</v>
       </c>
       <c r="R3" t="n">
-        <v>6507689.400664413</v>
+        <v>6507771</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2005-08-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2005-08-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,74 +853,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>ek-hassellund</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Amanda Sjölund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Amanda Sjölund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>160788</v>
+        <v>126648791</v>
       </c>
       <c r="B4" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>311</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>MÄSELNOMRÅDET, Ög</t>
+          <t>Översätter, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541653.9428826337</v>
+        <v>541804</v>
       </c>
       <c r="R4" t="n">
-        <v>6507597.34783431</v>
+        <v>6507631</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +934,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Växte fläckvis på basen av en ek</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,35 +956,25 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Karlsson</t>
+          <t>Jonatan Axelsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Sällsynta lavar i Östergötland 2000</t>
-        </is>
-      </c>
+          <t>Jonatan Axelsson, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1571027</v>
+        <v>105911436</v>
       </c>
       <c r="B5" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56827</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,37 +982,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5445</v>
+        <v>100087</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ängen O, nära kraftledningen, Ög</t>
+          <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541420.1842529235</v>
+        <v>541777</v>
       </c>
       <c r="R5" t="n">
-        <v>6507894.116983887</v>
+        <v>6507969</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,22 +1049,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2011-04-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2011-04-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,79 +1065,77 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Lövskog med ek, asp och Salix</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>ek</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>Amanda Sjölund</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>Amanda Sjölund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97309085</v>
+        <v>105911424</v>
       </c>
       <c r="B6" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3884</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541798.4683894962</v>
+        <v>541901</v>
       </c>
       <c r="R6" t="n">
-        <v>6507856.085942249</v>
+        <v>6507862</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,22 +1159,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97309068</v>
+        <v>105911447</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56840</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,37 +1202,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>206000</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gråskimlig fladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Vespertilio murinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541676.7466041126</v>
+        <v>541924</v>
       </c>
       <c r="R7" t="n">
-        <v>6507946.217709351</v>
+        <v>6507841</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,22 +1269,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,15 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97309067</v>
+        <v>97309093</v>
       </c>
       <c r="B8" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>107609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>219686</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541721.9325611682</v>
+        <v>541781</v>
       </c>
       <c r="R8" t="n">
-        <v>6507906.698204139</v>
+        <v>6507822</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1445,19 +1369,9 @@
           <t>2021-06-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,53 +1398,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97309069</v>
+        <v>3916143</v>
       </c>
       <c r="B9" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>102225</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>221223</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Finspång, Ög</t>
+          <t>Finspång, strax NV om Översätter, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541771.178516068</v>
+        <v>541855</v>
       </c>
       <c r="R9" t="n">
-        <v>6507973.728429741</v>
+        <v>6507689</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1554,22 +1463,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-08-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-08-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,53 +1479,53 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>ek-hassellund</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97309093</v>
+        <v>97309086</v>
       </c>
       <c r="B10" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219686</v>
+        <v>221235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1636,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541781.1424162245</v>
+        <v>541914</v>
       </c>
       <c r="R10" t="n">
-        <v>6507821.609091413</v>
+        <v>6507806</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1669,19 +1568,9 @@
           <t>2021-06-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,15 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97309086</v>
+        <v>5021320</v>
       </c>
       <c r="B11" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,37 +1608,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Finspång, Ög</t>
+          <t>Finspång, strax NV om Översätter, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541914.0337022943</v>
+        <v>541855</v>
       </c>
       <c r="R11" t="n">
-        <v>6507806.414983729</v>
+        <v>6507689</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,22 +1662,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-08-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-08-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,82 +1678,69 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>ek-hassellund</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105911424</v>
+        <v>97309067</v>
       </c>
       <c r="B12" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205998</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541901.4639377473</v>
+        <v>541722</v>
       </c>
       <c r="R12" t="n">
-        <v>6507861.871572202</v>
+        <v>6507907</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1903,22 +1764,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
           <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1945,10 +1796,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105911447</v>
+        <v>97309068</v>
       </c>
       <c r="B13" t="n">
-        <v>56620</v>
+        <v>101326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,50 +1807,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>206000</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gråskimlig fladdermus</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Vespertilio murinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541924</v>
+        <v>541677</v>
       </c>
       <c r="R13" t="n">
-        <v>6507841</v>
+        <v>6507946</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2023,7 +1861,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2055,66 +1893,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105911436</v>
+        <v>97309069</v>
       </c>
       <c r="B14" t="n">
-        <v>57495</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Dokumentation efterfrågas</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100087</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541777.4794122044</v>
+        <v>541771</v>
       </c>
       <c r="R14" t="n">
-        <v>6507968.600850282</v>
+        <v>6507973</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2138,22 +1958,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
           <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2177,108 +1987,6 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>126648791</v>
-      </c>
-      <c r="B15" t="n">
-        <v>80117</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Översätter, Ög</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>541804</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6507631</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Finspång</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Risinge</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växte fläckvis på basen av en ek</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Jonatan Axelsson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Jonatan Axelsson, Gabriel Johansson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57690-2022 artfynd.xlsx
+++ b/artfynd/A 57690-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97309085</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97309087</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126648791</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911436</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911424</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911447</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1395,6 +1430,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97309093</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1497,6 +1537,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3916143</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1594,6 +1639,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97309086</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1696,6 +1746,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5021320</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1793,6 +1848,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97309067</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1890,6 +1950,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97309068</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,8 +2052,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97309069</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>